--- a/templates/HEADWAY_SIGNALLING_v1.0.xlsx
+++ b/templates/HEADWAY_SIGNALLING_v1.0.xlsx
@@ -562,7 +562,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>3. Row 3 contains an illustrative example row (marked with ID 'EXAMPLE_*'). Replace or delete before production use.</t>
+          <t>3. Row 3 contains a minimal valid baseline network for demonstration purposes. You may modify or replace it with your own railway data. The example is designed to load without validation errors.</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="A3:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"GENERIC_FIXED_BLOCK_ENGINEERING_MODEL,ETCS_LEVEL_2,CBTC_MOVING_BLOCK"</formula1>
+      <formula1>"GENERIC_FIXED_BLOCK_ENGINEERING_MODEL,ETCS_LEVEL_2,ETCS_LEVEL_2_ENGINEERING_MODEL,CBTC_MOVING_BLOCK,CBTC_MOVING_BLOCK_ENGINEERING_MODEL"</formula1>
     </dataValidation>
     <dataValidation sqref="B3:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TWO_ASPECT,THREE_ASPECT,FOUR_ASPECT"</formula1>
@@ -868,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -968,6 +968,34 @@
         </is>
       </c>
       <c r="F3" s="10" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>SIG_02</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>LNK_01</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>NOMINAL</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="n">
         <v>200</v>
       </c>
     </row>

--- a/templates/HEADWAY_SIGNALLING_v1.0.xlsx
+++ b/templates/HEADWAY_SIGNALLING_v1.0.xlsx
@@ -12,7 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SignallingSystem" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signals" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blocks" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InterlockingRoutes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlockGeometry" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TVSGeometry" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InterlockingRoutes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -508,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="85" customWidth="1" min="1" max="1"/>
@@ -588,38 +590,59 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>7. For multi-link signalling blocks or TVS sections, define spatial geometry intervals in the 'BlockGeometry' or 'TVSGeometry' worksheet with sequential numbering.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>WORKSHEET INVENTORY:</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>• SignallingSystem: Global signalling system configuration</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>• Signals: Physical and virtual wayside signals</t>
+          <t>• SignallingSystem: Global signalling system configuration</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>• Blocks: Fixed signalling block sections</t>
+          <t>• Signals: Physical and virtual wayside signals</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>• Blocks: Fixed signalling block sections</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>• BlockGeometry: Multi-link spatial interval geometry for signalling blocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>• TVSGeometry: Multi-link spatial interval geometry for Tunnel Ventilation Sections</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>• InterlockingRoutes: Interlocking train routes and conflicting paths</t>
         </is>
@@ -1018,17 +1041,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1049,25 +1069,10 @@
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>LINK_ID</t>
+          <t>OVERLAP_M</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>START_OFFSET_M</t>
-        </is>
-      </c>
-      <c r="F1" s="8" t="inlineStr">
-        <is>
-          <t>END_OFFSET_M</t>
-        </is>
-      </c>
-      <c r="G1" s="8" t="inlineStr">
-        <is>
-          <t>OVERLAP_M</t>
-        </is>
-      </c>
-      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>RELEASE_DELAY_S</t>
         </is>
@@ -1091,25 +1096,10 @@
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>(Required)</t>
+          <t>[m]</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>[m]</t>
-        </is>
-      </c>
-      <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t>[m]</t>
-        </is>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>[m]</t>
-        </is>
-      </c>
-      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>[s]</t>
         </is>
@@ -1131,21 +1121,10 @@
           <t>SIG_02</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>LNK_01</t>
-        </is>
+      <c r="D3" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="F3" s="10" t="n">
-        <v>1100</v>
-      </c>
-      <c r="G3" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="H3" s="10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1155,6 +1134,198 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>BLOCK_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>SEQUENCE</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>LINK_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>START_OFFSET_M</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>END_OFFSET_M</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>(Required)</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>(Required)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>(Required)</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>[m]</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>[m]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>BLK_01</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>LNK_01</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>TVS_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>SEQUENCE</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>LINK_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>START_OFFSET_M</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>END_OFFSET_M</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>(Required)</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>(Required)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>(Required)</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>[m]</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>[m]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>TVS_01</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>LNK_01</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
